--- a/data/import/AMPHI.xlsx
+++ b/data/import/AMPHI.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC635A8-1337-4EDA-A512-AA2B06B2A50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555D87A-0C07-4816-8445-BBF4981D52DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="1719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="1727">
   <si>
     <t>06 61 42 80 85</t>
   </si>
@@ -5174,6 +5174,30 @@
   </si>
   <si>
     <t>حموي علمي 3</t>
+  </si>
+  <si>
+    <t>خلف الله اميرة</t>
+  </si>
+  <si>
+    <t>BON 45(07/10/2026)</t>
+  </si>
+  <si>
+    <t>فراد يسرى</t>
+  </si>
+  <si>
+    <t>BON 605 (07/10/2026)</t>
+  </si>
+  <si>
+    <t>رامي سندس</t>
+  </si>
+  <si>
+    <t>BON 606 (07/10/2026)</t>
+  </si>
+  <si>
+    <t>BON 607 (07/10/2026)</t>
+  </si>
+  <si>
+    <t>BON 608 (07/10/2026)</t>
   </si>
 </sst>
 </file>
@@ -5503,9 +5527,6 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -5513,6 +5534,9 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -5854,7 +5878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L1022"/>
+  <dimension ref="A1:L1026"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -5864,34 +5888,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="20"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9028,34 +9052,34 @@
       <c r="L137" s="7"/>
     </row>
     <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="18"/>
-      <c r="B140" s="18"/>
-      <c r="C140" s="18"/>
-      <c r="D140" s="18"/>
-      <c r="E140" s="18"/>
-      <c r="F140" s="18"/>
-      <c r="G140" s="18"/>
-      <c r="H140" s="18"/>
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
-      <c r="K140" s="18"/>
-      <c r="L140" s="18"/>
+      <c r="A140" s="21"/>
+      <c r="B140" s="21"/>
+      <c r="C140" s="21"/>
+      <c r="D140" s="21"/>
+      <c r="E140" s="21"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
+      <c r="I140" s="21"/>
+      <c r="J140" s="21"/>
+      <c r="K140" s="21"/>
+      <c r="L140" s="21"/>
     </row>
     <row r="141" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="19" t="s">
+      <c r="A141" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="B141" s="20"/>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20"/>
-      <c r="E141" s="20"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
-      <c r="I141" s="20"/>
-      <c r="J141" s="20"/>
-      <c r="K141" s="20"/>
-      <c r="L141" s="21"/>
+      <c r="B141" s="19"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="19"/>
+      <c r="E141" s="19"/>
+      <c r="F141" s="19"/>
+      <c r="G141" s="19"/>
+      <c r="H141" s="19"/>
+      <c r="I141" s="19"/>
+      <c r="J141" s="19"/>
+      <c r="K141" s="19"/>
+      <c r="L141" s="20"/>
     </row>
     <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
@@ -11286,34 +11310,34 @@
       <c r="L238" s="7"/>
     </row>
     <row r="241" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="18"/>
-      <c r="B241" s="18"/>
-      <c r="C241" s="18"/>
-      <c r="D241" s="18"/>
-      <c r="E241" s="18"/>
-      <c r="F241" s="18"/>
-      <c r="G241" s="18"/>
-      <c r="H241" s="18"/>
-      <c r="I241" s="18"/>
-      <c r="J241" s="18"/>
-      <c r="K241" s="18"/>
-      <c r="L241" s="18"/>
+      <c r="A241" s="21"/>
+      <c r="B241" s="21"/>
+      <c r="C241" s="21"/>
+      <c r="D241" s="21"/>
+      <c r="E241" s="21"/>
+      <c r="F241" s="21"/>
+      <c r="G241" s="21"/>
+      <c r="H241" s="21"/>
+      <c r="I241" s="21"/>
+      <c r="J241" s="21"/>
+      <c r="K241" s="21"/>
+      <c r="L241" s="21"/>
     </row>
     <row r="242" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="19" t="s">
+      <c r="A242" s="18" t="s">
         <v>539</v>
       </c>
-      <c r="B242" s="20"/>
-      <c r="C242" s="20"/>
-      <c r="D242" s="20"/>
-      <c r="E242" s="20"/>
-      <c r="F242" s="20"/>
-      <c r="G242" s="20"/>
-      <c r="H242" s="20"/>
-      <c r="I242" s="20"/>
-      <c r="J242" s="20"/>
-      <c r="K242" s="20"/>
-      <c r="L242" s="21"/>
+      <c r="B242" s="19"/>
+      <c r="C242" s="19"/>
+      <c r="D242" s="19"/>
+      <c r="E242" s="19"/>
+      <c r="F242" s="19"/>
+      <c r="G242" s="19"/>
+      <c r="H242" s="19"/>
+      <c r="I242" s="19"/>
+      <c r="J242" s="19"/>
+      <c r="K242" s="19"/>
+      <c r="L242" s="20"/>
     </row>
     <row r="243" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
@@ -13174,7 +13198,9 @@
       <c r="D322" s="9">
         <v>3000</v>
       </c>
-      <c r="E322" s="9"/>
+      <c r="E322" s="9">
+        <v>3000</v>
+      </c>
       <c r="F322" s="9"/>
       <c r="G322" s="9"/>
       <c r="H322" s="7"/>
@@ -13192,7 +13218,9 @@
       <c r="D323" s="6" t="s">
         <v>764</v>
       </c>
-      <c r="E323" s="6"/>
+      <c r="E323" s="6" t="s">
+        <v>1725</v>
+      </c>
       <c r="F323" s="6"/>
       <c r="G323" s="6"/>
       <c r="H323" s="7"/>
@@ -13686,7 +13714,9 @@
       <c r="D346" s="9">
         <v>3000</v>
       </c>
-      <c r="E346" s="9"/>
+      <c r="E346" s="9">
+        <v>3000</v>
+      </c>
       <c r="F346" s="9"/>
       <c r="G346" s="9"/>
       <c r="H346" s="7"/>
@@ -13704,7 +13734,9 @@
       <c r="D347" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="E347" s="6"/>
+      <c r="E347" s="6" t="s">
+        <v>1726</v>
+      </c>
       <c r="F347" s="6"/>
       <c r="G347" s="6"/>
       <c r="H347" s="7"/>
@@ -13986,28 +14018,28 @@
       <c r="L361" s="7"/>
     </row>
     <row r="364" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="18"/>
-      <c r="B364" s="18"/>
-      <c r="C364" s="18"/>
-      <c r="D364" s="18"/>
-      <c r="E364" s="18"/>
-      <c r="F364" s="18"/>
-      <c r="G364" s="18"/>
-      <c r="H364" s="18"/>
-      <c r="I364" s="18"/>
+      <c r="A364" s="21"/>
+      <c r="B364" s="21"/>
+      <c r="C364" s="21"/>
+      <c r="D364" s="21"/>
+      <c r="E364" s="21"/>
+      <c r="F364" s="21"/>
+      <c r="G364" s="21"/>
+      <c r="H364" s="21"/>
+      <c r="I364" s="21"/>
     </row>
     <row r="365" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="19" t="s">
+      <c r="A365" s="18" t="s">
         <v>778</v>
       </c>
-      <c r="B365" s="20"/>
-      <c r="C365" s="20"/>
-      <c r="D365" s="20"/>
-      <c r="E365" s="20"/>
-      <c r="F365" s="20"/>
-      <c r="G365" s="20"/>
-      <c r="H365" s="20"/>
-      <c r="I365" s="21"/>
+      <c r="B365" s="19"/>
+      <c r="C365" s="19"/>
+      <c r="D365" s="19"/>
+      <c r="E365" s="19"/>
+      <c r="F365" s="19"/>
+      <c r="G365" s="19"/>
+      <c r="H365" s="19"/>
+      <c r="I365" s="20"/>
     </row>
     <row r="366" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
@@ -15189,28 +15221,28 @@
       <c r="I438" s="7"/>
     </row>
     <row r="441" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="18"/>
-      <c r="B441" s="18"/>
-      <c r="C441" s="18"/>
-      <c r="D441" s="18"/>
-      <c r="E441" s="18"/>
-      <c r="F441" s="18"/>
-      <c r="G441" s="18"/>
-      <c r="H441" s="18"/>
-      <c r="I441" s="18"/>
+      <c r="A441" s="21"/>
+      <c r="B441" s="21"/>
+      <c r="C441" s="21"/>
+      <c r="D441" s="21"/>
+      <c r="E441" s="21"/>
+      <c r="F441" s="21"/>
+      <c r="G441" s="21"/>
+      <c r="H441" s="21"/>
+      <c r="I441" s="21"/>
     </row>
     <row r="442" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="19" t="s">
+      <c r="A442" s="18" t="s">
         <v>858</v>
       </c>
-      <c r="B442" s="20"/>
-      <c r="C442" s="20"/>
-      <c r="D442" s="20"/>
-      <c r="E442" s="20"/>
-      <c r="F442" s="20"/>
-      <c r="G442" s="20"/>
-      <c r="H442" s="20"/>
-      <c r="I442" s="21"/>
+      <c r="B442" s="19"/>
+      <c r="C442" s="19"/>
+      <c r="D442" s="19"/>
+      <c r="E442" s="19"/>
+      <c r="F442" s="19"/>
+      <c r="G442" s="19"/>
+      <c r="H442" s="19"/>
+      <c r="I442" s="20"/>
     </row>
     <row r="443" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
@@ -16592,28 +16624,28 @@
       <c r="I523" s="7"/>
     </row>
     <row r="526" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="18"/>
-      <c r="B526" s="18"/>
-      <c r="C526" s="18"/>
-      <c r="D526" s="18"/>
-      <c r="E526" s="18"/>
-      <c r="F526" s="18"/>
-      <c r="G526" s="18"/>
-      <c r="H526" s="18"/>
-      <c r="I526" s="18"/>
+      <c r="A526" s="21"/>
+      <c r="B526" s="21"/>
+      <c r="C526" s="21"/>
+      <c r="D526" s="21"/>
+      <c r="E526" s="21"/>
+      <c r="F526" s="21"/>
+      <c r="G526" s="21"/>
+      <c r="H526" s="21"/>
+      <c r="I526" s="21"/>
     </row>
     <row r="527" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="19" t="s">
+      <c r="A527" s="18" t="s">
         <v>963</v>
       </c>
-      <c r="B527" s="20"/>
-      <c r="C527" s="20"/>
-      <c r="D527" s="20"/>
-      <c r="E527" s="20"/>
-      <c r="F527" s="20"/>
-      <c r="G527" s="20"/>
-      <c r="H527" s="20"/>
-      <c r="I527" s="21"/>
+      <c r="B527" s="19"/>
+      <c r="C527" s="19"/>
+      <c r="D527" s="19"/>
+      <c r="E527" s="19"/>
+      <c r="F527" s="19"/>
+      <c r="G527" s="19"/>
+      <c r="H527" s="19"/>
+      <c r="I527" s="20"/>
     </row>
     <row r="528" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
@@ -18341,28 +18373,28 @@
       <c r="I632" s="7"/>
     </row>
     <row r="635" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A635" s="18"/>
-      <c r="B635" s="18"/>
-      <c r="C635" s="18"/>
-      <c r="D635" s="18"/>
-      <c r="E635" s="18"/>
-      <c r="F635" s="18"/>
-      <c r="G635" s="18"/>
-      <c r="H635" s="18"/>
-      <c r="I635" s="18"/>
+      <c r="A635" s="21"/>
+      <c r="B635" s="21"/>
+      <c r="C635" s="21"/>
+      <c r="D635" s="21"/>
+      <c r="E635" s="21"/>
+      <c r="F635" s="21"/>
+      <c r="G635" s="21"/>
+      <c r="H635" s="21"/>
+      <c r="I635" s="21"/>
     </row>
     <row r="636" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A636" s="19" t="s">
+      <c r="A636" s="18" t="s">
         <v>1222</v>
       </c>
-      <c r="B636" s="20"/>
-      <c r="C636" s="20"/>
-      <c r="D636" s="20"/>
-      <c r="E636" s="20"/>
-      <c r="F636" s="20"/>
-      <c r="G636" s="20"/>
-      <c r="H636" s="20"/>
-      <c r="I636" s="21"/>
+      <c r="B636" s="19"/>
+      <c r="C636" s="19"/>
+      <c r="D636" s="19"/>
+      <c r="E636" s="19"/>
+      <c r="F636" s="19"/>
+      <c r="G636" s="19"/>
+      <c r="H636" s="19"/>
+      <c r="I636" s="20"/>
     </row>
     <row r="637" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
@@ -19842,28 +19874,28 @@
       <c r="I725" s="7"/>
     </row>
     <row r="728" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A728" s="18"/>
-      <c r="B728" s="18"/>
-      <c r="C728" s="18"/>
-      <c r="D728" s="18"/>
-      <c r="E728" s="18"/>
-      <c r="F728" s="18"/>
-      <c r="G728" s="18"/>
-      <c r="H728" s="18"/>
-      <c r="I728" s="18"/>
+      <c r="A728" s="21"/>
+      <c r="B728" s="21"/>
+      <c r="C728" s="21"/>
+      <c r="D728" s="21"/>
+      <c r="E728" s="21"/>
+      <c r="F728" s="21"/>
+      <c r="G728" s="21"/>
+      <c r="H728" s="21"/>
+      <c r="I728" s="21"/>
     </row>
     <row r="729" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A729" s="19" t="s">
+      <c r="A729" s="18" t="s">
         <v>1223</v>
       </c>
-      <c r="B729" s="20"/>
-      <c r="C729" s="20"/>
-      <c r="D729" s="20"/>
-      <c r="E729" s="20"/>
-      <c r="F729" s="20"/>
-      <c r="G729" s="20"/>
-      <c r="H729" s="20"/>
-      <c r="I729" s="21"/>
+      <c r="B729" s="19"/>
+      <c r="C729" s="19"/>
+      <c r="D729" s="19"/>
+      <c r="E729" s="19"/>
+      <c r="F729" s="19"/>
+      <c r="G729" s="19"/>
+      <c r="H729" s="19"/>
+      <c r="I729" s="20"/>
     </row>
     <row r="730" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
@@ -20551,28 +20583,28 @@
       <c r="I770" s="7"/>
     </row>
     <row r="773" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A773" s="18"/>
-      <c r="B773" s="18"/>
-      <c r="C773" s="18"/>
-      <c r="D773" s="18"/>
-      <c r="E773" s="18"/>
-      <c r="F773" s="18"/>
-      <c r="G773" s="18"/>
-      <c r="H773" s="18"/>
-      <c r="I773" s="18"/>
+      <c r="A773" s="21"/>
+      <c r="B773" s="21"/>
+      <c r="C773" s="21"/>
+      <c r="D773" s="21"/>
+      <c r="E773" s="21"/>
+      <c r="F773" s="21"/>
+      <c r="G773" s="21"/>
+      <c r="H773" s="21"/>
+      <c r="I773" s="21"/>
     </row>
     <row r="774" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A774" s="19" t="s">
+      <c r="A774" s="18" t="s">
         <v>1261</v>
       </c>
-      <c r="B774" s="20"/>
-      <c r="C774" s="20"/>
-      <c r="D774" s="20"/>
-      <c r="E774" s="20"/>
-      <c r="F774" s="20"/>
-      <c r="G774" s="20"/>
-      <c r="H774" s="20"/>
-      <c r="I774" s="21"/>
+      <c r="B774" s="19"/>
+      <c r="C774" s="19"/>
+      <c r="D774" s="19"/>
+      <c r="E774" s="19"/>
+      <c r="F774" s="19"/>
+      <c r="G774" s="19"/>
+      <c r="H774" s="19"/>
+      <c r="I774" s="20"/>
     </row>
     <row r="775" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
@@ -22402,34 +22434,34 @@
       <c r="I883" s="7"/>
     </row>
     <row r="886" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A886" s="18"/>
-      <c r="B886" s="18"/>
-      <c r="C886" s="18"/>
-      <c r="D886" s="18"/>
-      <c r="E886" s="18"/>
-      <c r="F886" s="18"/>
-      <c r="G886" s="18"/>
-      <c r="H886" s="18"/>
-      <c r="I886" s="18"/>
-      <c r="J886" s="18"/>
-      <c r="K886" s="18"/>
-      <c r="L886" s="18"/>
+      <c r="A886" s="21"/>
+      <c r="B886" s="21"/>
+      <c r="C886" s="21"/>
+      <c r="D886" s="21"/>
+      <c r="E886" s="21"/>
+      <c r="F886" s="21"/>
+      <c r="G886" s="21"/>
+      <c r="H886" s="21"/>
+      <c r="I886" s="21"/>
+      <c r="J886" s="21"/>
+      <c r="K886" s="21"/>
+      <c r="L886" s="21"/>
     </row>
     <row r="887" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A887" s="19" t="s">
+      <c r="A887" s="18" t="s">
         <v>1718</v>
       </c>
-      <c r="B887" s="20"/>
-      <c r="C887" s="20"/>
-      <c r="D887" s="20"/>
-      <c r="E887" s="20"/>
-      <c r="F887" s="20"/>
-      <c r="G887" s="20"/>
-      <c r="H887" s="20"/>
-      <c r="I887" s="20"/>
-      <c r="J887" s="20"/>
-      <c r="K887" s="20"/>
-      <c r="L887" s="21"/>
+      <c r="B887" s="19"/>
+      <c r="C887" s="19"/>
+      <c r="D887" s="19"/>
+      <c r="E887" s="19"/>
+      <c r="F887" s="19"/>
+      <c r="G887" s="19"/>
+      <c r="H887" s="19"/>
+      <c r="I887" s="19"/>
+      <c r="J887" s="19"/>
+      <c r="K887" s="19"/>
+      <c r="L887" s="20"/>
     </row>
     <row r="888" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
@@ -24692,28 +24724,28 @@
       <c r="L998" s="7"/>
     </row>
     <row r="1001" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1001" s="18"/>
-      <c r="B1001" s="18"/>
-      <c r="C1001" s="18"/>
-      <c r="D1001" s="18"/>
-      <c r="E1001" s="18"/>
-      <c r="F1001" s="18"/>
-      <c r="G1001" s="18"/>
-      <c r="H1001" s="18"/>
-      <c r="I1001" s="18"/>
+      <c r="A1001" s="21"/>
+      <c r="B1001" s="21"/>
+      <c r="C1001" s="21"/>
+      <c r="D1001" s="21"/>
+      <c r="E1001" s="21"/>
+      <c r="F1001" s="21"/>
+      <c r="G1001" s="21"/>
+      <c r="H1001" s="21"/>
+      <c r="I1001" s="21"/>
     </row>
     <row r="1002" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1002" s="19" t="s">
+      <c r="A1002" s="18" t="s">
         <v>1567</v>
       </c>
-      <c r="B1002" s="20"/>
-      <c r="C1002" s="20"/>
-      <c r="D1002" s="20"/>
-      <c r="E1002" s="20"/>
-      <c r="F1002" s="20"/>
-      <c r="G1002" s="20"/>
-      <c r="H1002" s="20"/>
-      <c r="I1002" s="21"/>
+      <c r="B1002" s="19"/>
+      <c r="C1002" s="19"/>
+      <c r="D1002" s="19"/>
+      <c r="E1002" s="19"/>
+      <c r="F1002" s="19"/>
+      <c r="G1002" s="19"/>
+      <c r="H1002" s="19"/>
+      <c r="I1002" s="20"/>
     </row>
     <row r="1003" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1003" s="1" t="s">
@@ -24803,28 +24835,28 @@
       <c r="I1007" s="7"/>
     </row>
     <row r="1010" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1010" s="18"/>
-      <c r="B1010" s="18"/>
-      <c r="C1010" s="18"/>
-      <c r="D1010" s="18"/>
-      <c r="E1010" s="18"/>
-      <c r="F1010" s="18"/>
-      <c r="G1010" s="18"/>
-      <c r="H1010" s="18"/>
-      <c r="I1010" s="18"/>
+      <c r="A1010" s="21"/>
+      <c r="B1010" s="21"/>
+      <c r="C1010" s="21"/>
+      <c r="D1010" s="21"/>
+      <c r="E1010" s="21"/>
+      <c r="F1010" s="21"/>
+      <c r="G1010" s="21"/>
+      <c r="H1010" s="21"/>
+      <c r="I1010" s="21"/>
     </row>
     <row r="1011" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1011" s="19" t="s">
+      <c r="A1011" s="18" t="s">
         <v>1572</v>
       </c>
-      <c r="B1011" s="20"/>
-      <c r="C1011" s="20"/>
-      <c r="D1011" s="20"/>
-      <c r="E1011" s="20"/>
-      <c r="F1011" s="20"/>
-      <c r="G1011" s="20"/>
-      <c r="H1011" s="20"/>
-      <c r="I1011" s="21"/>
+      <c r="B1011" s="19"/>
+      <c r="C1011" s="19"/>
+      <c r="D1011" s="19"/>
+      <c r="E1011" s="19"/>
+      <c r="F1011" s="19"/>
+      <c r="G1011" s="19"/>
+      <c r="H1011" s="19"/>
+      <c r="I1011" s="20"/>
     </row>
     <row r="1012" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1012" s="1" t="s">
@@ -24997,8 +25029,74 @@
       <c r="H1022" s="7"/>
       <c r="I1022" s="7"/>
     </row>
+    <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1023" s="15" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1023" s="8"/>
+      <c r="C1023" s="9">
+        <v>250</v>
+      </c>
+      <c r="D1023" s="9">
+        <v>3000</v>
+      </c>
+      <c r="E1023" s="9"/>
+      <c r="F1023" s="9"/>
+      <c r="G1023" s="7"/>
+      <c r="H1023" s="7"/>
+      <c r="I1023" s="7"/>
+    </row>
+    <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1024" s="16"/>
+      <c r="B1024" s="5"/>
+      <c r="C1024" s="6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="D1024" s="6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E1024" s="6"/>
+      <c r="F1024" s="6"/>
+      <c r="G1024" s="7"/>
+      <c r="H1024" s="7"/>
+      <c r="I1024" s="7"/>
+    </row>
+    <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1025" s="15" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1025" s="8"/>
+      <c r="C1025" s="9">
+        <v>250</v>
+      </c>
+      <c r="D1025" s="9">
+        <v>3000</v>
+      </c>
+      <c r="E1025" s="9"/>
+      <c r="F1025" s="9"/>
+      <c r="G1025" s="7"/>
+      <c r="H1025" s="7"/>
+      <c r="I1025" s="7"/>
+    </row>
+    <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1026" s="16"/>
+      <c r="B1026" s="5"/>
+      <c r="C1026" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D1026" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="E1026" s="6"/>
+      <c r="F1026" s="6"/>
+      <c r="G1026" s="7"/>
+      <c r="H1026" s="7"/>
+      <c r="I1026" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="506">
+  <mergeCells count="508">
+    <mergeCell ref="A1023:A1024"/>
+    <mergeCell ref="A1025:A1026"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
@@ -25513,7 +25611,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F660878-7891-415C-8F9B-B0DE34BC7DA5}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -25523,28 +25621,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1582</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -25630,28 +25728,28 @@
       <c r="I7" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
     </row>
     <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>1585</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="21"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -26668,8 +26766,40 @@
       <c r="H74" s="7"/>
       <c r="I74" s="7"/>
     </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="9">
+        <v>250</v>
+      </c>
+      <c r="D75" s="9">
+        <v>2000</v>
+      </c>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="7"/>
+      <c r="H75" s="7"/>
+      <c r="I75" s="7"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="6" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>1720</v>
+      </c>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="7"/>
+      <c r="H76" s="7"/>
+      <c r="I76" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="A11:I11"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
@@ -26700,6 +26830,7 @@
     <mergeCell ref="A53:A54"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A75:A76"/>
     <mergeCell ref="A73:A74"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="A63:A64"/>
@@ -26724,31 +26855,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18"/>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
     </row>
     <row r="2" spans="1:12" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1658</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="21"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -27616,28 +27747,28 @@
       <c r="I55" s="7"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="18"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
     </row>
     <row r="59" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="19" t="s">
+      <c r="A59" s="18" t="s">
         <v>1713</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="21"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="20"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">

--- a/data/import/AMPHI.xlsx
+++ b/data/import/AMPHI.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5555D87A-0C07-4816-8445-BBF4981D52DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2093BC1-CE13-40C3-971A-39CCC9169669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BAC" sheetId="2" r:id="rId1"/>
@@ -5155,9 +5155,6 @@
     <t>نموشي بسملة</t>
   </si>
   <si>
-    <t>BON 19(03 /10/2026)</t>
-  </si>
-  <si>
     <t>دراجي 1 ثانوي</t>
   </si>
   <si>
@@ -5198,6 +5195,9 @@
   </si>
   <si>
     <t>BON 608 (07/10/2026)</t>
+  </si>
+  <si>
+    <t>BON19(03/10/2026)</t>
   </si>
 </sst>
 </file>
@@ -5527,6 +5527,9 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
@@ -5534,9 +5537,6 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -5888,34 +5888,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
     </row>
     <row r="2" spans="1:12" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="21"/>
     </row>
     <row r="3" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9052,34 +9052,34 @@
       <c r="L137" s="7"/>
     </row>
     <row r="140" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="21"/>
-      <c r="B140" s="21"/>
-      <c r="C140" s="21"/>
-      <c r="D140" s="21"/>
-      <c r="E140" s="21"/>
-      <c r="F140" s="21"/>
-      <c r="G140" s="21"/>
-      <c r="H140" s="21"/>
-      <c r="I140" s="21"/>
-      <c r="J140" s="21"/>
-      <c r="K140" s="21"/>
-      <c r="L140" s="21"/>
+      <c r="A140" s="18"/>
+      <c r="B140" s="18"/>
+      <c r="C140" s="18"/>
+      <c r="D140" s="18"/>
+      <c r="E140" s="18"/>
+      <c r="F140" s="18"/>
+      <c r="G140" s="18"/>
+      <c r="H140" s="18"/>
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+      <c r="K140" s="18"/>
+      <c r="L140" s="18"/>
     </row>
     <row r="141" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="18" t="s">
+      <c r="A141" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="B141" s="19"/>
-      <c r="C141" s="19"/>
-      <c r="D141" s="19"/>
-      <c r="E141" s="19"/>
-      <c r="F141" s="19"/>
-      <c r="G141" s="19"/>
-      <c r="H141" s="19"/>
-      <c r="I141" s="19"/>
-      <c r="J141" s="19"/>
-      <c r="K141" s="19"/>
-      <c r="L141" s="20"/>
+      <c r="B141" s="20"/>
+      <c r="C141" s="20"/>
+      <c r="D141" s="20"/>
+      <c r="E141" s="20"/>
+      <c r="F141" s="20"/>
+      <c r="G141" s="20"/>
+      <c r="H141" s="20"/>
+      <c r="I141" s="20"/>
+      <c r="J141" s="20"/>
+      <c r="K141" s="20"/>
+      <c r="L141" s="21"/>
     </row>
     <row r="142" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
@@ -11310,34 +11310,34 @@
       <c r="L238" s="7"/>
     </row>
     <row r="241" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="21"/>
-      <c r="B241" s="21"/>
-      <c r="C241" s="21"/>
-      <c r="D241" s="21"/>
-      <c r="E241" s="21"/>
-      <c r="F241" s="21"/>
-      <c r="G241" s="21"/>
-      <c r="H241" s="21"/>
-      <c r="I241" s="21"/>
-      <c r="J241" s="21"/>
-      <c r="K241" s="21"/>
-      <c r="L241" s="21"/>
+      <c r="A241" s="18"/>
+      <c r="B241" s="18"/>
+      <c r="C241" s="18"/>
+      <c r="D241" s="18"/>
+      <c r="E241" s="18"/>
+      <c r="F241" s="18"/>
+      <c r="G241" s="18"/>
+      <c r="H241" s="18"/>
+      <c r="I241" s="18"/>
+      <c r="J241" s="18"/>
+      <c r="K241" s="18"/>
+      <c r="L241" s="18"/>
     </row>
     <row r="242" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="18" t="s">
+      <c r="A242" s="19" t="s">
         <v>539</v>
       </c>
-      <c r="B242" s="19"/>
-      <c r="C242" s="19"/>
-      <c r="D242" s="19"/>
-      <c r="E242" s="19"/>
-      <c r="F242" s="19"/>
-      <c r="G242" s="19"/>
-      <c r="H242" s="19"/>
-      <c r="I242" s="19"/>
-      <c r="J242" s="19"/>
-      <c r="K242" s="19"/>
-      <c r="L242" s="20"/>
+      <c r="B242" s="20"/>
+      <c r="C242" s="20"/>
+      <c r="D242" s="20"/>
+      <c r="E242" s="20"/>
+      <c r="F242" s="20"/>
+      <c r="G242" s="20"/>
+      <c r="H242" s="20"/>
+      <c r="I242" s="20"/>
+      <c r="J242" s="20"/>
+      <c r="K242" s="20"/>
+      <c r="L242" s="21"/>
     </row>
     <row r="243" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
@@ -13219,7 +13219,7 @@
         <v>764</v>
       </c>
       <c r="E323" s="6" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="F323" s="6"/>
       <c r="G323" s="6"/>
@@ -13735,7 +13735,7 @@
         <v>773</v>
       </c>
       <c r="E347" s="6" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="F347" s="6"/>
       <c r="G347" s="6"/>
@@ -14018,28 +14018,28 @@
       <c r="L361" s="7"/>
     </row>
     <row r="364" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="21"/>
-      <c r="B364" s="21"/>
-      <c r="C364" s="21"/>
-      <c r="D364" s="21"/>
-      <c r="E364" s="21"/>
-      <c r="F364" s="21"/>
-      <c r="G364" s="21"/>
-      <c r="H364" s="21"/>
-      <c r="I364" s="21"/>
+      <c r="A364" s="18"/>
+      <c r="B364" s="18"/>
+      <c r="C364" s="18"/>
+      <c r="D364" s="18"/>
+      <c r="E364" s="18"/>
+      <c r="F364" s="18"/>
+      <c r="G364" s="18"/>
+      <c r="H364" s="18"/>
+      <c r="I364" s="18"/>
     </row>
     <row r="365" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="18" t="s">
+      <c r="A365" s="19" t="s">
         <v>778</v>
       </c>
-      <c r="B365" s="19"/>
-      <c r="C365" s="19"/>
-      <c r="D365" s="19"/>
-      <c r="E365" s="19"/>
-      <c r="F365" s="19"/>
-      <c r="G365" s="19"/>
-      <c r="H365" s="19"/>
-      <c r="I365" s="20"/>
+      <c r="B365" s="20"/>
+      <c r="C365" s="20"/>
+      <c r="D365" s="20"/>
+      <c r="E365" s="20"/>
+      <c r="F365" s="20"/>
+      <c r="G365" s="20"/>
+      <c r="H365" s="20"/>
+      <c r="I365" s="21"/>
     </row>
     <row r="366" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
@@ -15221,28 +15221,28 @@
       <c r="I438" s="7"/>
     </row>
     <row r="441" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A441" s="21"/>
-      <c r="B441" s="21"/>
-      <c r="C441" s="21"/>
-      <c r="D441" s="21"/>
-      <c r="E441" s="21"/>
-      <c r="F441" s="21"/>
-      <c r="G441" s="21"/>
-      <c r="H441" s="21"/>
-      <c r="I441" s="21"/>
+      <c r="A441" s="18"/>
+      <c r="B441" s="18"/>
+      <c r="C441" s="18"/>
+      <c r="D441" s="18"/>
+      <c r="E441" s="18"/>
+      <c r="F441" s="18"/>
+      <c r="G441" s="18"/>
+      <c r="H441" s="18"/>
+      <c r="I441" s="18"/>
     </row>
     <row r="442" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A442" s="18" t="s">
+      <c r="A442" s="19" t="s">
         <v>858</v>
       </c>
-      <c r="B442" s="19"/>
-      <c r="C442" s="19"/>
-      <c r="D442" s="19"/>
-      <c r="E442" s="19"/>
-      <c r="F442" s="19"/>
-      <c r="G442" s="19"/>
-      <c r="H442" s="19"/>
-      <c r="I442" s="20"/>
+      <c r="B442" s="20"/>
+      <c r="C442" s="20"/>
+      <c r="D442" s="20"/>
+      <c r="E442" s="20"/>
+      <c r="F442" s="20"/>
+      <c r="G442" s="20"/>
+      <c r="H442" s="20"/>
+      <c r="I442" s="21"/>
     </row>
     <row r="443" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
@@ -16624,28 +16624,28 @@
       <c r="I523" s="7"/>
     </row>
     <row r="526" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A526" s="21"/>
-      <c r="B526" s="21"/>
-      <c r="C526" s="21"/>
-      <c r="D526" s="21"/>
-      <c r="E526" s="21"/>
-      <c r="F526" s="21"/>
-      <c r="G526" s="21"/>
-      <c r="H526" s="21"/>
-      <c r="I526" s="21"/>
+      <c r="A526" s="18"/>
+      <c r="B526" s="18"/>
+      <c r="C526" s="18"/>
+      <c r="D526" s="18"/>
+      <c r="E526" s="18"/>
+      <c r="F526" s="18"/>
+      <c r="G526" s="18"/>
+      <c r="H526" s="18"/>
+      <c r="I526" s="18"/>
     </row>
     <row r="527" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A527" s="18" t="s">
+      <c r="A527" s="19" t="s">
         <v>963</v>
       </c>
-      <c r="B527" s="19"/>
-      <c r="C527" s="19"/>
-      <c r="D527" s="19"/>
-      <c r="E527" s="19"/>
-      <c r="F527" s="19"/>
-      <c r="G527" s="19"/>
-      <c r="H527" s="19"/>
-      <c r="I527" s="20"/>
+      <c r="B527" s="20"/>
+      <c r="C527" s="20"/>
+      <c r="D527" s="20"/>
+      <c r="E527" s="20"/>
+      <c r="F527" s="20"/>
+      <c r="G527" s="20"/>
+      <c r="H527" s="20"/>
+      <c r="I527" s="21"/>
     </row>
     <row r="528" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
@@ -18373,28 +18373,28 @@
       <c r="I632" s="7"/>
     </row>
     <row r="635" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A635" s="21"/>
-      <c r="B635" s="21"/>
-      <c r="C635" s="21"/>
-      <c r="D635" s="21"/>
-      <c r="E635" s="21"/>
-      <c r="F635" s="21"/>
-      <c r="G635" s="21"/>
-      <c r="H635" s="21"/>
-      <c r="I635" s="21"/>
+      <c r="A635" s="18"/>
+      <c r="B635" s="18"/>
+      <c r="C635" s="18"/>
+      <c r="D635" s="18"/>
+      <c r="E635" s="18"/>
+      <c r="F635" s="18"/>
+      <c r="G635" s="18"/>
+      <c r="H635" s="18"/>
+      <c r="I635" s="18"/>
     </row>
     <row r="636" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A636" s="18" t="s">
+      <c r="A636" s="19" t="s">
         <v>1222</v>
       </c>
-      <c r="B636" s="19"/>
-      <c r="C636" s="19"/>
-      <c r="D636" s="19"/>
-      <c r="E636" s="19"/>
-      <c r="F636" s="19"/>
-      <c r="G636" s="19"/>
-      <c r="H636" s="19"/>
-      <c r="I636" s="20"/>
+      <c r="B636" s="20"/>
+      <c r="C636" s="20"/>
+      <c r="D636" s="20"/>
+      <c r="E636" s="20"/>
+      <c r="F636" s="20"/>
+      <c r="G636" s="20"/>
+      <c r="H636" s="20"/>
+      <c r="I636" s="21"/>
     </row>
     <row r="637" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1" t="s">
@@ -19874,28 +19874,28 @@
       <c r="I725" s="7"/>
     </row>
     <row r="728" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A728" s="21"/>
-      <c r="B728" s="21"/>
-      <c r="C728" s="21"/>
-      <c r="D728" s="21"/>
-      <c r="E728" s="21"/>
-      <c r="F728" s="21"/>
-      <c r="G728" s="21"/>
-      <c r="H728" s="21"/>
-      <c r="I728" s="21"/>
+      <c r="A728" s="18"/>
+      <c r="B728" s="18"/>
+      <c r="C728" s="18"/>
+      <c r="D728" s="18"/>
+      <c r="E728" s="18"/>
+      <c r="F728" s="18"/>
+      <c r="G728" s="18"/>
+      <c r="H728" s="18"/>
+      <c r="I728" s="18"/>
     </row>
     <row r="729" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A729" s="18" t="s">
+      <c r="A729" s="19" t="s">
         <v>1223</v>
       </c>
-      <c r="B729" s="19"/>
-      <c r="C729" s="19"/>
-      <c r="D729" s="19"/>
-      <c r="E729" s="19"/>
-      <c r="F729" s="19"/>
-      <c r="G729" s="19"/>
-      <c r="H729" s="19"/>
-      <c r="I729" s="20"/>
+      <c r="B729" s="20"/>
+      <c r="C729" s="20"/>
+      <c r="D729" s="20"/>
+      <c r="E729" s="20"/>
+      <c r="F729" s="20"/>
+      <c r="G729" s="20"/>
+      <c r="H729" s="20"/>
+      <c r="I729" s="21"/>
     </row>
     <row r="730" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
@@ -20583,28 +20583,28 @@
       <c r="I770" s="7"/>
     </row>
     <row r="773" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A773" s="21"/>
-      <c r="B773" s="21"/>
-      <c r="C773" s="21"/>
-      <c r="D773" s="21"/>
-      <c r="E773" s="21"/>
-      <c r="F773" s="21"/>
-      <c r="G773" s="21"/>
-      <c r="H773" s="21"/>
-      <c r="I773" s="21"/>
+      <c r="A773" s="18"/>
+      <c r="B773" s="18"/>
+      <c r="C773" s="18"/>
+      <c r="D773" s="18"/>
+      <c r="E773" s="18"/>
+      <c r="F773" s="18"/>
+      <c r="G773" s="18"/>
+      <c r="H773" s="18"/>
+      <c r="I773" s="18"/>
     </row>
     <row r="774" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A774" s="18" t="s">
+      <c r="A774" s="19" t="s">
         <v>1261</v>
       </c>
-      <c r="B774" s="19"/>
-      <c r="C774" s="19"/>
-      <c r="D774" s="19"/>
-      <c r="E774" s="19"/>
-      <c r="F774" s="19"/>
-      <c r="G774" s="19"/>
-      <c r="H774" s="19"/>
-      <c r="I774" s="20"/>
+      <c r="B774" s="20"/>
+      <c r="C774" s="20"/>
+      <c r="D774" s="20"/>
+      <c r="E774" s="20"/>
+      <c r="F774" s="20"/>
+      <c r="G774" s="20"/>
+      <c r="H774" s="20"/>
+      <c r="I774" s="21"/>
     </row>
     <row r="775" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A775" s="1" t="s">
@@ -22434,34 +22434,34 @@
       <c r="I883" s="7"/>
     </row>
     <row r="886" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A886" s="21"/>
-      <c r="B886" s="21"/>
-      <c r="C886" s="21"/>
-      <c r="D886" s="21"/>
-      <c r="E886" s="21"/>
-      <c r="F886" s="21"/>
-      <c r="G886" s="21"/>
-      <c r="H886" s="21"/>
-      <c r="I886" s="21"/>
-      <c r="J886" s="21"/>
-      <c r="K886" s="21"/>
-      <c r="L886" s="21"/>
+      <c r="A886" s="18"/>
+      <c r="B886" s="18"/>
+      <c r="C886" s="18"/>
+      <c r="D886" s="18"/>
+      <c r="E886" s="18"/>
+      <c r="F886" s="18"/>
+      <c r="G886" s="18"/>
+      <c r="H886" s="18"/>
+      <c r="I886" s="18"/>
+      <c r="J886" s="18"/>
+      <c r="K886" s="18"/>
+      <c r="L886" s="18"/>
     </row>
     <row r="887" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A887" s="18" t="s">
-        <v>1718</v>
-      </c>
-      <c r="B887" s="19"/>
-      <c r="C887" s="19"/>
-      <c r="D887" s="19"/>
-      <c r="E887" s="19"/>
-      <c r="F887" s="19"/>
-      <c r="G887" s="19"/>
-      <c r="H887" s="19"/>
-      <c r="I887" s="19"/>
-      <c r="J887" s="19"/>
-      <c r="K887" s="19"/>
-      <c r="L887" s="20"/>
+      <c r="A887" s="19" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B887" s="20"/>
+      <c r="C887" s="20"/>
+      <c r="D887" s="20"/>
+      <c r="E887" s="20"/>
+      <c r="F887" s="20"/>
+      <c r="G887" s="20"/>
+      <c r="H887" s="20"/>
+      <c r="I887" s="20"/>
+      <c r="J887" s="20"/>
+      <c r="K887" s="20"/>
+      <c r="L887" s="21"/>
     </row>
     <row r="888" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A888" s="1" t="s">
@@ -24724,28 +24724,28 @@
       <c r="L998" s="7"/>
     </row>
     <row r="1001" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1001" s="21"/>
-      <c r="B1001" s="21"/>
-      <c r="C1001" s="21"/>
-      <c r="D1001" s="21"/>
-      <c r="E1001" s="21"/>
-      <c r="F1001" s="21"/>
-      <c r="G1001" s="21"/>
-      <c r="H1001" s="21"/>
-      <c r="I1001" s="21"/>
+      <c r="A1001" s="18"/>
+      <c r="B1001" s="18"/>
+      <c r="C1001" s="18"/>
+      <c r="D1001" s="18"/>
+      <c r="E1001" s="18"/>
+      <c r="F1001" s="18"/>
+      <c r="G1001" s="18"/>
+      <c r="H1001" s="18"/>
+      <c r="I1001" s="18"/>
     </row>
     <row r="1002" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1002" s="18" t="s">
+      <c r="A1002" s="19" t="s">
         <v>1567</v>
       </c>
-      <c r="B1002" s="19"/>
-      <c r="C1002" s="19"/>
-      <c r="D1002" s="19"/>
-      <c r="E1002" s="19"/>
-      <c r="F1002" s="19"/>
-      <c r="G1002" s="19"/>
-      <c r="H1002" s="19"/>
-      <c r="I1002" s="20"/>
+      <c r="B1002" s="20"/>
+      <c r="C1002" s="20"/>
+      <c r="D1002" s="20"/>
+      <c r="E1002" s="20"/>
+      <c r="F1002" s="20"/>
+      <c r="G1002" s="20"/>
+      <c r="H1002" s="20"/>
+      <c r="I1002" s="21"/>
     </row>
     <row r="1003" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1003" s="1" t="s">
@@ -24835,28 +24835,28 @@
       <c r="I1007" s="7"/>
     </row>
     <row r="1010" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1010" s="21"/>
-      <c r="B1010" s="21"/>
-      <c r="C1010" s="21"/>
-      <c r="D1010" s="21"/>
-      <c r="E1010" s="21"/>
-      <c r="F1010" s="21"/>
-      <c r="G1010" s="21"/>
-      <c r="H1010" s="21"/>
-      <c r="I1010" s="21"/>
+      <c r="A1010" s="18"/>
+      <c r="B1010" s="18"/>
+      <c r="C1010" s="18"/>
+      <c r="D1010" s="18"/>
+      <c r="E1010" s="18"/>
+      <c r="F1010" s="18"/>
+      <c r="G1010" s="18"/>
+      <c r="H1010" s="18"/>
+      <c r="I1010" s="18"/>
     </row>
     <row r="1011" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1011" s="18" t="s">
+      <c r="A1011" s="19" t="s">
         <v>1572</v>
       </c>
-      <c r="B1011" s="19"/>
-      <c r="C1011" s="19"/>
-      <c r="D1011" s="19"/>
-      <c r="E1011" s="19"/>
-      <c r="F1011" s="19"/>
-      <c r="G1011" s="19"/>
-      <c r="H1011" s="19"/>
-      <c r="I1011" s="20"/>
+      <c r="B1011" s="20"/>
+      <c r="C1011" s="20"/>
+      <c r="D1011" s="20"/>
+      <c r="E1011" s="20"/>
+      <c r="F1011" s="20"/>
+      <c r="G1011" s="20"/>
+      <c r="H1011" s="20"/>
+      <c r="I1011" s="21"/>
     </row>
     <row r="1012" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1012" s="1" t="s">
@@ -25031,7 +25031,7 @@
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" s="15" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B1023" s="8"/>
       <c r="C1023" s="9">
@@ -25050,10 +25050,10 @@
       <c r="A1024" s="16"/>
       <c r="B1024" s="5"/>
       <c r="C1024" s="6" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D1024" s="6" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="E1024" s="6"/>
       <c r="F1024" s="6"/>
@@ -25063,7 +25063,7 @@
     </row>
     <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" s="15" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B1025" s="8"/>
       <c r="C1025" s="9">
@@ -25082,10 +25082,10 @@
       <c r="A1026" s="16"/>
       <c r="B1026" s="5"/>
       <c r="C1026" s="6" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D1026" s="6" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="E1026" s="6"/>
       <c r="F1026" s="6"/>
@@ -25095,6 +25095,490 @@
     </row>
   </sheetData>
   <mergeCells count="508">
+    <mergeCell ref="A1017:A1018"/>
+    <mergeCell ref="A1019:A1020"/>
+    <mergeCell ref="A1021:A1022"/>
+    <mergeCell ref="A1006:A1007"/>
+    <mergeCell ref="A1013:A1014"/>
+    <mergeCell ref="A1015:A1016"/>
+    <mergeCell ref="A1010:I1010"/>
+    <mergeCell ref="A1011:I1011"/>
+    <mergeCell ref="A995:A996"/>
+    <mergeCell ref="A997:A998"/>
+    <mergeCell ref="A1001:I1001"/>
+    <mergeCell ref="A1002:I1002"/>
+    <mergeCell ref="A1004:A1005"/>
+    <mergeCell ref="A985:A986"/>
+    <mergeCell ref="A987:A988"/>
+    <mergeCell ref="A989:A990"/>
+    <mergeCell ref="A991:A992"/>
+    <mergeCell ref="A993:A994"/>
+    <mergeCell ref="A975:A976"/>
+    <mergeCell ref="A977:A978"/>
+    <mergeCell ref="A979:A980"/>
+    <mergeCell ref="A981:A982"/>
+    <mergeCell ref="A983:A984"/>
+    <mergeCell ref="A967:A968"/>
+    <mergeCell ref="A969:A970"/>
+    <mergeCell ref="A971:A972"/>
+    <mergeCell ref="A973:A974"/>
+    <mergeCell ref="A957:A958"/>
+    <mergeCell ref="A959:A960"/>
+    <mergeCell ref="A961:A962"/>
+    <mergeCell ref="A963:A964"/>
+    <mergeCell ref="A965:A966"/>
+    <mergeCell ref="A947:A948"/>
+    <mergeCell ref="A949:A950"/>
+    <mergeCell ref="A951:A952"/>
+    <mergeCell ref="A953:A954"/>
+    <mergeCell ref="A955:A956"/>
+    <mergeCell ref="A937:A938"/>
+    <mergeCell ref="A939:A940"/>
+    <mergeCell ref="A941:A942"/>
+    <mergeCell ref="A943:A944"/>
+    <mergeCell ref="A945:A946"/>
+    <mergeCell ref="A927:A928"/>
+    <mergeCell ref="A929:A930"/>
+    <mergeCell ref="A931:A932"/>
+    <mergeCell ref="A933:A934"/>
+    <mergeCell ref="A935:A936"/>
+    <mergeCell ref="A917:A918"/>
+    <mergeCell ref="A919:A920"/>
+    <mergeCell ref="A921:A922"/>
+    <mergeCell ref="A923:A924"/>
+    <mergeCell ref="A925:A926"/>
+    <mergeCell ref="A907:A908"/>
+    <mergeCell ref="A909:A910"/>
+    <mergeCell ref="A911:A912"/>
+    <mergeCell ref="A913:A914"/>
+    <mergeCell ref="A915:A916"/>
+    <mergeCell ref="A897:A898"/>
+    <mergeCell ref="A899:A900"/>
+    <mergeCell ref="A901:A902"/>
+    <mergeCell ref="A903:A904"/>
+    <mergeCell ref="A905:A906"/>
+    <mergeCell ref="A891:A892"/>
+    <mergeCell ref="A886:L886"/>
+    <mergeCell ref="A887:L887"/>
+    <mergeCell ref="A893:A894"/>
+    <mergeCell ref="A895:A896"/>
+    <mergeCell ref="A880:A881"/>
+    <mergeCell ref="A882:A883"/>
+    <mergeCell ref="A889:A890"/>
+    <mergeCell ref="A870:A871"/>
+    <mergeCell ref="A872:A873"/>
+    <mergeCell ref="A874:A875"/>
+    <mergeCell ref="A876:A877"/>
+    <mergeCell ref="A878:A879"/>
+    <mergeCell ref="A860:A861"/>
+    <mergeCell ref="A862:A863"/>
+    <mergeCell ref="A864:A865"/>
+    <mergeCell ref="A866:A867"/>
+    <mergeCell ref="A868:A869"/>
+    <mergeCell ref="A850:A851"/>
+    <mergeCell ref="A852:A853"/>
+    <mergeCell ref="A854:A855"/>
+    <mergeCell ref="A856:A857"/>
+    <mergeCell ref="A858:A859"/>
+    <mergeCell ref="A840:A841"/>
+    <mergeCell ref="A842:A843"/>
+    <mergeCell ref="A844:A845"/>
+    <mergeCell ref="A846:A847"/>
+    <mergeCell ref="A848:A849"/>
+    <mergeCell ref="A830:A831"/>
+    <mergeCell ref="A832:A833"/>
+    <mergeCell ref="A834:A835"/>
+    <mergeCell ref="A836:A837"/>
+    <mergeCell ref="A838:A839"/>
+    <mergeCell ref="A820:A821"/>
+    <mergeCell ref="A822:A823"/>
+    <mergeCell ref="A824:A825"/>
+    <mergeCell ref="A826:A827"/>
+    <mergeCell ref="A828:A829"/>
+    <mergeCell ref="A810:A811"/>
+    <mergeCell ref="A812:A813"/>
+    <mergeCell ref="A814:A815"/>
+    <mergeCell ref="A816:A817"/>
+    <mergeCell ref="A818:A819"/>
+    <mergeCell ref="A800:A801"/>
+    <mergeCell ref="A802:A803"/>
+    <mergeCell ref="A804:A805"/>
+    <mergeCell ref="A806:A807"/>
+    <mergeCell ref="A808:A809"/>
+    <mergeCell ref="A790:A791"/>
+    <mergeCell ref="A792:A793"/>
+    <mergeCell ref="A794:A795"/>
+    <mergeCell ref="A796:A797"/>
+    <mergeCell ref="A798:A799"/>
+    <mergeCell ref="A780:A781"/>
+    <mergeCell ref="A782:A783"/>
+    <mergeCell ref="A784:A785"/>
+    <mergeCell ref="A786:A787"/>
+    <mergeCell ref="A788:A789"/>
+    <mergeCell ref="A776:A777"/>
+    <mergeCell ref="A778:A779"/>
+    <mergeCell ref="A773:I773"/>
+    <mergeCell ref="A774:I774"/>
+    <mergeCell ref="A763:A764"/>
+    <mergeCell ref="A765:A766"/>
+    <mergeCell ref="A767:A768"/>
+    <mergeCell ref="A769:A770"/>
+    <mergeCell ref="A753:A754"/>
+    <mergeCell ref="A755:A756"/>
+    <mergeCell ref="A757:A758"/>
+    <mergeCell ref="A759:A760"/>
+    <mergeCell ref="A761:A762"/>
+    <mergeCell ref="A743:A744"/>
+    <mergeCell ref="A745:A746"/>
+    <mergeCell ref="A747:A748"/>
+    <mergeCell ref="A749:A750"/>
+    <mergeCell ref="A751:A752"/>
+    <mergeCell ref="A733:A734"/>
+    <mergeCell ref="A735:A736"/>
+    <mergeCell ref="A737:A738"/>
+    <mergeCell ref="A739:A740"/>
+    <mergeCell ref="A741:A742"/>
+    <mergeCell ref="A722:A723"/>
+    <mergeCell ref="A724:A725"/>
+    <mergeCell ref="A728:I728"/>
+    <mergeCell ref="A729:I729"/>
+    <mergeCell ref="A731:A732"/>
+    <mergeCell ref="A712:A713"/>
+    <mergeCell ref="A714:A715"/>
+    <mergeCell ref="A716:A717"/>
+    <mergeCell ref="A718:A719"/>
+    <mergeCell ref="A720:A721"/>
+    <mergeCell ref="A702:A703"/>
+    <mergeCell ref="A704:A705"/>
+    <mergeCell ref="A706:A707"/>
+    <mergeCell ref="A708:A709"/>
+    <mergeCell ref="A710:A711"/>
+    <mergeCell ref="A692:A693"/>
+    <mergeCell ref="A694:A695"/>
+    <mergeCell ref="A696:A697"/>
+    <mergeCell ref="A698:A699"/>
+    <mergeCell ref="A700:A701"/>
+    <mergeCell ref="A682:A683"/>
+    <mergeCell ref="A684:A685"/>
+    <mergeCell ref="A686:A687"/>
+    <mergeCell ref="A688:A689"/>
+    <mergeCell ref="A690:A691"/>
+    <mergeCell ref="A672:A673"/>
+    <mergeCell ref="A674:A675"/>
+    <mergeCell ref="A676:A677"/>
+    <mergeCell ref="A678:A679"/>
+    <mergeCell ref="A680:A681"/>
+    <mergeCell ref="A662:A663"/>
+    <mergeCell ref="A664:A665"/>
+    <mergeCell ref="A666:A667"/>
+    <mergeCell ref="A668:A669"/>
+    <mergeCell ref="A670:A671"/>
+    <mergeCell ref="A652:A653"/>
+    <mergeCell ref="A654:A655"/>
+    <mergeCell ref="A656:A657"/>
+    <mergeCell ref="A658:A659"/>
+    <mergeCell ref="A660:A661"/>
+    <mergeCell ref="A642:A643"/>
+    <mergeCell ref="A644:A645"/>
+    <mergeCell ref="A646:A647"/>
+    <mergeCell ref="A648:A649"/>
+    <mergeCell ref="A650:A651"/>
+    <mergeCell ref="A631:A632"/>
+    <mergeCell ref="A635:I635"/>
+    <mergeCell ref="A636:I636"/>
+    <mergeCell ref="A638:A639"/>
+    <mergeCell ref="A640:A641"/>
+    <mergeCell ref="A621:A622"/>
+    <mergeCell ref="A623:A624"/>
+    <mergeCell ref="A625:A626"/>
+    <mergeCell ref="A627:A628"/>
+    <mergeCell ref="A629:A630"/>
+    <mergeCell ref="A611:A612"/>
+    <mergeCell ref="A613:A614"/>
+    <mergeCell ref="A615:A616"/>
+    <mergeCell ref="A617:A618"/>
+    <mergeCell ref="A619:A620"/>
+    <mergeCell ref="A601:A602"/>
+    <mergeCell ref="A603:A604"/>
+    <mergeCell ref="A605:A606"/>
+    <mergeCell ref="A607:A608"/>
+    <mergeCell ref="A609:A610"/>
+    <mergeCell ref="A591:A592"/>
+    <mergeCell ref="A593:A594"/>
+    <mergeCell ref="A595:A596"/>
+    <mergeCell ref="A597:A598"/>
+    <mergeCell ref="A599:A600"/>
+    <mergeCell ref="A581:A582"/>
+    <mergeCell ref="A583:A584"/>
+    <mergeCell ref="A585:A586"/>
+    <mergeCell ref="A587:A588"/>
+    <mergeCell ref="A589:A590"/>
+    <mergeCell ref="A571:A572"/>
+    <mergeCell ref="A573:A574"/>
+    <mergeCell ref="A575:A576"/>
+    <mergeCell ref="A577:A578"/>
+    <mergeCell ref="A579:A580"/>
+    <mergeCell ref="A561:A562"/>
+    <mergeCell ref="A563:A564"/>
+    <mergeCell ref="A565:A566"/>
+    <mergeCell ref="A567:A568"/>
+    <mergeCell ref="A569:A570"/>
+    <mergeCell ref="A551:A552"/>
+    <mergeCell ref="A553:A554"/>
+    <mergeCell ref="A555:A556"/>
+    <mergeCell ref="A557:A558"/>
+    <mergeCell ref="A559:A560"/>
+    <mergeCell ref="A541:A542"/>
+    <mergeCell ref="A543:A544"/>
+    <mergeCell ref="A545:A546"/>
+    <mergeCell ref="A547:A548"/>
+    <mergeCell ref="A549:A550"/>
+    <mergeCell ref="A531:A532"/>
+    <mergeCell ref="A533:A534"/>
+    <mergeCell ref="A535:A536"/>
+    <mergeCell ref="A537:A538"/>
+    <mergeCell ref="A539:A540"/>
+    <mergeCell ref="A522:A523"/>
+    <mergeCell ref="A526:I526"/>
+    <mergeCell ref="A527:I527"/>
+    <mergeCell ref="A529:A530"/>
+    <mergeCell ref="A512:A513"/>
+    <mergeCell ref="A514:A515"/>
+    <mergeCell ref="A516:A517"/>
+    <mergeCell ref="A518:A519"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="A502:A503"/>
+    <mergeCell ref="A504:A505"/>
+    <mergeCell ref="A506:A507"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="A510:A511"/>
+    <mergeCell ref="A492:A493"/>
+    <mergeCell ref="A494:A495"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="A498:A499"/>
+    <mergeCell ref="A500:A501"/>
+    <mergeCell ref="A482:A483"/>
+    <mergeCell ref="A484:A485"/>
+    <mergeCell ref="A486:A487"/>
+    <mergeCell ref="A488:A489"/>
+    <mergeCell ref="A490:A491"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="A474:A475"/>
+    <mergeCell ref="A476:A477"/>
+    <mergeCell ref="A478:A479"/>
+    <mergeCell ref="A480:A481"/>
+    <mergeCell ref="A462:A463"/>
+    <mergeCell ref="A464:A465"/>
+    <mergeCell ref="A466:A467"/>
+    <mergeCell ref="A468:A469"/>
+    <mergeCell ref="A470:A471"/>
+    <mergeCell ref="A452:A453"/>
+    <mergeCell ref="A454:A455"/>
+    <mergeCell ref="A456:A457"/>
+    <mergeCell ref="A458:A459"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="A442:I442"/>
+    <mergeCell ref="A444:A445"/>
+    <mergeCell ref="A446:A447"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="A450:A451"/>
+    <mergeCell ref="A431:A432"/>
+    <mergeCell ref="A433:A434"/>
+    <mergeCell ref="A435:A436"/>
+    <mergeCell ref="A437:A438"/>
+    <mergeCell ref="A441:I441"/>
+    <mergeCell ref="A421:A422"/>
+    <mergeCell ref="A423:A424"/>
+    <mergeCell ref="A425:A426"/>
+    <mergeCell ref="A427:A428"/>
+    <mergeCell ref="A429:A430"/>
+    <mergeCell ref="A411:A412"/>
+    <mergeCell ref="A413:A414"/>
+    <mergeCell ref="A415:A416"/>
+    <mergeCell ref="A417:A418"/>
+    <mergeCell ref="A419:A420"/>
+    <mergeCell ref="A401:A402"/>
+    <mergeCell ref="A403:A404"/>
+    <mergeCell ref="A405:A406"/>
+    <mergeCell ref="A407:A408"/>
+    <mergeCell ref="A409:A410"/>
+    <mergeCell ref="A391:A392"/>
+    <mergeCell ref="A393:A394"/>
+    <mergeCell ref="A395:A396"/>
+    <mergeCell ref="A397:A398"/>
+    <mergeCell ref="A399:A400"/>
+    <mergeCell ref="A381:A382"/>
+    <mergeCell ref="A383:A384"/>
+    <mergeCell ref="A385:A386"/>
+    <mergeCell ref="A387:A388"/>
+    <mergeCell ref="A389:A390"/>
+    <mergeCell ref="A371:A372"/>
+    <mergeCell ref="A373:A374"/>
+    <mergeCell ref="A375:A376"/>
+    <mergeCell ref="A377:A378"/>
+    <mergeCell ref="A379:A380"/>
+    <mergeCell ref="A367:A368"/>
+    <mergeCell ref="A369:A370"/>
+    <mergeCell ref="A364:I364"/>
+    <mergeCell ref="A365:I365"/>
+    <mergeCell ref="A352:A353"/>
+    <mergeCell ref="A354:A355"/>
+    <mergeCell ref="A356:A357"/>
+    <mergeCell ref="A358:A359"/>
+    <mergeCell ref="A360:A361"/>
+    <mergeCell ref="A342:A343"/>
+    <mergeCell ref="A344:A345"/>
+    <mergeCell ref="A346:A347"/>
+    <mergeCell ref="A348:A349"/>
+    <mergeCell ref="A350:A351"/>
+    <mergeCell ref="A332:A333"/>
+    <mergeCell ref="A334:A335"/>
+    <mergeCell ref="A336:A337"/>
+    <mergeCell ref="A338:A339"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="A322:A323"/>
+    <mergeCell ref="A324:A325"/>
+    <mergeCell ref="A326:A327"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="A330:A331"/>
+    <mergeCell ref="A314:A315"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="A318:A319"/>
+    <mergeCell ref="A320:A321"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="A306:A307"/>
+    <mergeCell ref="A308:A309"/>
+    <mergeCell ref="A310:A311"/>
+    <mergeCell ref="A312:A313"/>
+    <mergeCell ref="A294:A295"/>
+    <mergeCell ref="A296:A297"/>
+    <mergeCell ref="A298:A299"/>
+    <mergeCell ref="A300:A301"/>
+    <mergeCell ref="A302:A303"/>
+    <mergeCell ref="A284:A285"/>
+    <mergeCell ref="A286:A287"/>
+    <mergeCell ref="A288:A289"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A274:A275"/>
+    <mergeCell ref="A276:A277"/>
+    <mergeCell ref="A278:A279"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A282:A283"/>
+    <mergeCell ref="A264:A265"/>
+    <mergeCell ref="A266:A267"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="A272:A273"/>
+    <mergeCell ref="A254:A255"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="A258:A259"/>
+    <mergeCell ref="A260:A261"/>
+    <mergeCell ref="A262:A263"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="A246:A247"/>
+    <mergeCell ref="A248:A249"/>
+    <mergeCell ref="A250:A251"/>
+    <mergeCell ref="A252:A253"/>
+    <mergeCell ref="A233:A234"/>
+    <mergeCell ref="A235:A236"/>
+    <mergeCell ref="A237:A238"/>
+    <mergeCell ref="A241:L241"/>
+    <mergeCell ref="A242:L242"/>
+    <mergeCell ref="A223:A224"/>
+    <mergeCell ref="A225:A226"/>
+    <mergeCell ref="A227:A228"/>
+    <mergeCell ref="A229:A230"/>
+    <mergeCell ref="A231:A232"/>
+    <mergeCell ref="A213:A214"/>
+    <mergeCell ref="A215:A216"/>
+    <mergeCell ref="A217:A218"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="A221:A222"/>
+    <mergeCell ref="A203:A204"/>
+    <mergeCell ref="A205:A206"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A209:A210"/>
+    <mergeCell ref="A211:A212"/>
+    <mergeCell ref="A193:A194"/>
+    <mergeCell ref="A195:A196"/>
+    <mergeCell ref="A197:A198"/>
+    <mergeCell ref="A199:A200"/>
+    <mergeCell ref="A201:A202"/>
+    <mergeCell ref="A183:A184"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A187:A188"/>
+    <mergeCell ref="A189:A190"/>
+    <mergeCell ref="A191:A192"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="A177:A178"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A163:A164"/>
+    <mergeCell ref="A165:A166"/>
+    <mergeCell ref="A167:A168"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A153:A154"/>
+    <mergeCell ref="A155:A156"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="A159:A160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="A145:A146"/>
+    <mergeCell ref="A147:A148"/>
+    <mergeCell ref="A149:A150"/>
+    <mergeCell ref="A151:A152"/>
+    <mergeCell ref="A132:A133"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="A136:A137"/>
+    <mergeCell ref="A140:L140"/>
+    <mergeCell ref="A141:L141"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A128:A129"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
     <mergeCell ref="A1023:A1024"/>
     <mergeCell ref="A1025:A1026"/>
     <mergeCell ref="A4:A5"/>
@@ -25119,490 +25603,6 @@
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="A50:A51"/>
     <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A122:A123"/>
-    <mergeCell ref="A124:A125"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A128:A129"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="A145:A146"/>
-    <mergeCell ref="A147:A148"/>
-    <mergeCell ref="A149:A150"/>
-    <mergeCell ref="A151:A152"/>
-    <mergeCell ref="A132:A133"/>
-    <mergeCell ref="A134:A135"/>
-    <mergeCell ref="A136:A137"/>
-    <mergeCell ref="A140:L140"/>
-    <mergeCell ref="A141:L141"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="A165:A166"/>
-    <mergeCell ref="A167:A168"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A153:A154"/>
-    <mergeCell ref="A155:A156"/>
-    <mergeCell ref="A157:A158"/>
-    <mergeCell ref="A159:A160"/>
-    <mergeCell ref="A161:A162"/>
-    <mergeCell ref="A183:A184"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="A177:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="A203:A204"/>
-    <mergeCell ref="A205:A206"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="A209:A210"/>
-    <mergeCell ref="A211:A212"/>
-    <mergeCell ref="A193:A194"/>
-    <mergeCell ref="A195:A196"/>
-    <mergeCell ref="A197:A198"/>
-    <mergeCell ref="A199:A200"/>
-    <mergeCell ref="A201:A202"/>
-    <mergeCell ref="A223:A224"/>
-    <mergeCell ref="A225:A226"/>
-    <mergeCell ref="A227:A228"/>
-    <mergeCell ref="A229:A230"/>
-    <mergeCell ref="A231:A232"/>
-    <mergeCell ref="A213:A214"/>
-    <mergeCell ref="A215:A216"/>
-    <mergeCell ref="A217:A218"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A221:A222"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="A246:A247"/>
-    <mergeCell ref="A248:A249"/>
-    <mergeCell ref="A250:A251"/>
-    <mergeCell ref="A252:A253"/>
-    <mergeCell ref="A233:A234"/>
-    <mergeCell ref="A235:A236"/>
-    <mergeCell ref="A237:A238"/>
-    <mergeCell ref="A241:L241"/>
-    <mergeCell ref="A242:L242"/>
-    <mergeCell ref="A264:A265"/>
-    <mergeCell ref="A266:A267"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="A272:A273"/>
-    <mergeCell ref="A254:A255"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="A260:A261"/>
-    <mergeCell ref="A262:A263"/>
-    <mergeCell ref="A284:A285"/>
-    <mergeCell ref="A286:A287"/>
-    <mergeCell ref="A288:A289"/>
-    <mergeCell ref="A290:A291"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A274:A275"/>
-    <mergeCell ref="A276:A277"/>
-    <mergeCell ref="A278:A279"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A282:A283"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="A306:A307"/>
-    <mergeCell ref="A308:A309"/>
-    <mergeCell ref="A310:A311"/>
-    <mergeCell ref="A312:A313"/>
-    <mergeCell ref="A294:A295"/>
-    <mergeCell ref="A296:A297"/>
-    <mergeCell ref="A298:A299"/>
-    <mergeCell ref="A300:A301"/>
-    <mergeCell ref="A302:A303"/>
-    <mergeCell ref="A322:A323"/>
-    <mergeCell ref="A324:A325"/>
-    <mergeCell ref="A326:A327"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="A330:A331"/>
-    <mergeCell ref="A314:A315"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="A318:A319"/>
-    <mergeCell ref="A320:A321"/>
-    <mergeCell ref="A342:A343"/>
-    <mergeCell ref="A344:A345"/>
-    <mergeCell ref="A346:A347"/>
-    <mergeCell ref="A348:A349"/>
-    <mergeCell ref="A350:A351"/>
-    <mergeCell ref="A332:A333"/>
-    <mergeCell ref="A334:A335"/>
-    <mergeCell ref="A336:A337"/>
-    <mergeCell ref="A338:A339"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="A367:A368"/>
-    <mergeCell ref="A369:A370"/>
-    <mergeCell ref="A364:I364"/>
-    <mergeCell ref="A365:I365"/>
-    <mergeCell ref="A352:A353"/>
-    <mergeCell ref="A354:A355"/>
-    <mergeCell ref="A356:A357"/>
-    <mergeCell ref="A358:A359"/>
-    <mergeCell ref="A360:A361"/>
-    <mergeCell ref="A381:A382"/>
-    <mergeCell ref="A383:A384"/>
-    <mergeCell ref="A385:A386"/>
-    <mergeCell ref="A387:A388"/>
-    <mergeCell ref="A389:A390"/>
-    <mergeCell ref="A371:A372"/>
-    <mergeCell ref="A373:A374"/>
-    <mergeCell ref="A375:A376"/>
-    <mergeCell ref="A377:A378"/>
-    <mergeCell ref="A379:A380"/>
-    <mergeCell ref="A401:A402"/>
-    <mergeCell ref="A403:A404"/>
-    <mergeCell ref="A405:A406"/>
-    <mergeCell ref="A407:A408"/>
-    <mergeCell ref="A409:A410"/>
-    <mergeCell ref="A391:A392"/>
-    <mergeCell ref="A393:A394"/>
-    <mergeCell ref="A395:A396"/>
-    <mergeCell ref="A397:A398"/>
-    <mergeCell ref="A399:A400"/>
-    <mergeCell ref="A421:A422"/>
-    <mergeCell ref="A423:A424"/>
-    <mergeCell ref="A425:A426"/>
-    <mergeCell ref="A427:A428"/>
-    <mergeCell ref="A429:A430"/>
-    <mergeCell ref="A411:A412"/>
-    <mergeCell ref="A413:A414"/>
-    <mergeCell ref="A415:A416"/>
-    <mergeCell ref="A417:A418"/>
-    <mergeCell ref="A419:A420"/>
-    <mergeCell ref="A442:I442"/>
-    <mergeCell ref="A444:A445"/>
-    <mergeCell ref="A446:A447"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="A450:A451"/>
-    <mergeCell ref="A431:A432"/>
-    <mergeCell ref="A433:A434"/>
-    <mergeCell ref="A435:A436"/>
-    <mergeCell ref="A437:A438"/>
-    <mergeCell ref="A441:I441"/>
-    <mergeCell ref="A462:A463"/>
-    <mergeCell ref="A464:A465"/>
-    <mergeCell ref="A466:A467"/>
-    <mergeCell ref="A468:A469"/>
-    <mergeCell ref="A470:A471"/>
-    <mergeCell ref="A452:A453"/>
-    <mergeCell ref="A454:A455"/>
-    <mergeCell ref="A456:A457"/>
-    <mergeCell ref="A458:A459"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="A482:A483"/>
-    <mergeCell ref="A484:A485"/>
-    <mergeCell ref="A486:A487"/>
-    <mergeCell ref="A488:A489"/>
-    <mergeCell ref="A490:A491"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="A474:A475"/>
-    <mergeCell ref="A476:A477"/>
-    <mergeCell ref="A478:A479"/>
-    <mergeCell ref="A480:A481"/>
-    <mergeCell ref="A502:A503"/>
-    <mergeCell ref="A504:A505"/>
-    <mergeCell ref="A506:A507"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="A510:A511"/>
-    <mergeCell ref="A492:A493"/>
-    <mergeCell ref="A494:A495"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="A498:A499"/>
-    <mergeCell ref="A500:A501"/>
-    <mergeCell ref="A522:A523"/>
-    <mergeCell ref="A526:I526"/>
-    <mergeCell ref="A527:I527"/>
-    <mergeCell ref="A529:A530"/>
-    <mergeCell ref="A512:A513"/>
-    <mergeCell ref="A514:A515"/>
-    <mergeCell ref="A516:A517"/>
-    <mergeCell ref="A518:A519"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="A541:A542"/>
-    <mergeCell ref="A543:A544"/>
-    <mergeCell ref="A545:A546"/>
-    <mergeCell ref="A547:A548"/>
-    <mergeCell ref="A549:A550"/>
-    <mergeCell ref="A531:A532"/>
-    <mergeCell ref="A533:A534"/>
-    <mergeCell ref="A535:A536"/>
-    <mergeCell ref="A537:A538"/>
-    <mergeCell ref="A539:A540"/>
-    <mergeCell ref="A561:A562"/>
-    <mergeCell ref="A563:A564"/>
-    <mergeCell ref="A565:A566"/>
-    <mergeCell ref="A567:A568"/>
-    <mergeCell ref="A569:A570"/>
-    <mergeCell ref="A551:A552"/>
-    <mergeCell ref="A553:A554"/>
-    <mergeCell ref="A555:A556"/>
-    <mergeCell ref="A557:A558"/>
-    <mergeCell ref="A559:A560"/>
-    <mergeCell ref="A581:A582"/>
-    <mergeCell ref="A583:A584"/>
-    <mergeCell ref="A585:A586"/>
-    <mergeCell ref="A587:A588"/>
-    <mergeCell ref="A589:A590"/>
-    <mergeCell ref="A571:A572"/>
-    <mergeCell ref="A573:A574"/>
-    <mergeCell ref="A575:A576"/>
-    <mergeCell ref="A577:A578"/>
-    <mergeCell ref="A579:A580"/>
-    <mergeCell ref="A601:A602"/>
-    <mergeCell ref="A603:A604"/>
-    <mergeCell ref="A605:A606"/>
-    <mergeCell ref="A607:A608"/>
-    <mergeCell ref="A609:A610"/>
-    <mergeCell ref="A591:A592"/>
-    <mergeCell ref="A593:A594"/>
-    <mergeCell ref="A595:A596"/>
-    <mergeCell ref="A597:A598"/>
-    <mergeCell ref="A599:A600"/>
-    <mergeCell ref="A621:A622"/>
-    <mergeCell ref="A623:A624"/>
-    <mergeCell ref="A625:A626"/>
-    <mergeCell ref="A627:A628"/>
-    <mergeCell ref="A629:A630"/>
-    <mergeCell ref="A611:A612"/>
-    <mergeCell ref="A613:A614"/>
-    <mergeCell ref="A615:A616"/>
-    <mergeCell ref="A617:A618"/>
-    <mergeCell ref="A619:A620"/>
-    <mergeCell ref="A642:A643"/>
-    <mergeCell ref="A644:A645"/>
-    <mergeCell ref="A646:A647"/>
-    <mergeCell ref="A648:A649"/>
-    <mergeCell ref="A650:A651"/>
-    <mergeCell ref="A631:A632"/>
-    <mergeCell ref="A635:I635"/>
-    <mergeCell ref="A636:I636"/>
-    <mergeCell ref="A638:A639"/>
-    <mergeCell ref="A640:A641"/>
-    <mergeCell ref="A662:A663"/>
-    <mergeCell ref="A664:A665"/>
-    <mergeCell ref="A666:A667"/>
-    <mergeCell ref="A668:A669"/>
-    <mergeCell ref="A670:A671"/>
-    <mergeCell ref="A652:A653"/>
-    <mergeCell ref="A654:A655"/>
-    <mergeCell ref="A656:A657"/>
-    <mergeCell ref="A658:A659"/>
-    <mergeCell ref="A660:A661"/>
-    <mergeCell ref="A682:A683"/>
-    <mergeCell ref="A684:A685"/>
-    <mergeCell ref="A686:A687"/>
-    <mergeCell ref="A688:A689"/>
-    <mergeCell ref="A690:A691"/>
-    <mergeCell ref="A672:A673"/>
-    <mergeCell ref="A674:A675"/>
-    <mergeCell ref="A676:A677"/>
-    <mergeCell ref="A678:A679"/>
-    <mergeCell ref="A680:A681"/>
-    <mergeCell ref="A702:A703"/>
-    <mergeCell ref="A704:A705"/>
-    <mergeCell ref="A706:A707"/>
-    <mergeCell ref="A708:A709"/>
-    <mergeCell ref="A710:A711"/>
-    <mergeCell ref="A692:A693"/>
-    <mergeCell ref="A694:A695"/>
-    <mergeCell ref="A696:A697"/>
-    <mergeCell ref="A698:A699"/>
-    <mergeCell ref="A700:A701"/>
-    <mergeCell ref="A722:A723"/>
-    <mergeCell ref="A724:A725"/>
-    <mergeCell ref="A728:I728"/>
-    <mergeCell ref="A729:I729"/>
-    <mergeCell ref="A731:A732"/>
-    <mergeCell ref="A712:A713"/>
-    <mergeCell ref="A714:A715"/>
-    <mergeCell ref="A716:A717"/>
-    <mergeCell ref="A718:A719"/>
-    <mergeCell ref="A720:A721"/>
-    <mergeCell ref="A743:A744"/>
-    <mergeCell ref="A745:A746"/>
-    <mergeCell ref="A747:A748"/>
-    <mergeCell ref="A749:A750"/>
-    <mergeCell ref="A751:A752"/>
-    <mergeCell ref="A733:A734"/>
-    <mergeCell ref="A735:A736"/>
-    <mergeCell ref="A737:A738"/>
-    <mergeCell ref="A739:A740"/>
-    <mergeCell ref="A741:A742"/>
-    <mergeCell ref="A763:A764"/>
-    <mergeCell ref="A765:A766"/>
-    <mergeCell ref="A767:A768"/>
-    <mergeCell ref="A769:A770"/>
-    <mergeCell ref="A753:A754"/>
-    <mergeCell ref="A755:A756"/>
-    <mergeCell ref="A757:A758"/>
-    <mergeCell ref="A759:A760"/>
-    <mergeCell ref="A761:A762"/>
-    <mergeCell ref="A780:A781"/>
-    <mergeCell ref="A782:A783"/>
-    <mergeCell ref="A784:A785"/>
-    <mergeCell ref="A786:A787"/>
-    <mergeCell ref="A788:A789"/>
-    <mergeCell ref="A776:A777"/>
-    <mergeCell ref="A778:A779"/>
-    <mergeCell ref="A773:I773"/>
-    <mergeCell ref="A774:I774"/>
-    <mergeCell ref="A800:A801"/>
-    <mergeCell ref="A802:A803"/>
-    <mergeCell ref="A804:A805"/>
-    <mergeCell ref="A806:A807"/>
-    <mergeCell ref="A808:A809"/>
-    <mergeCell ref="A790:A791"/>
-    <mergeCell ref="A792:A793"/>
-    <mergeCell ref="A794:A795"/>
-    <mergeCell ref="A796:A797"/>
-    <mergeCell ref="A798:A799"/>
-    <mergeCell ref="A820:A821"/>
-    <mergeCell ref="A822:A823"/>
-    <mergeCell ref="A824:A825"/>
-    <mergeCell ref="A826:A827"/>
-    <mergeCell ref="A828:A829"/>
-    <mergeCell ref="A810:A811"/>
-    <mergeCell ref="A812:A813"/>
-    <mergeCell ref="A814:A815"/>
-    <mergeCell ref="A816:A817"/>
-    <mergeCell ref="A818:A819"/>
-    <mergeCell ref="A840:A841"/>
-    <mergeCell ref="A842:A843"/>
-    <mergeCell ref="A844:A845"/>
-    <mergeCell ref="A846:A847"/>
-    <mergeCell ref="A848:A849"/>
-    <mergeCell ref="A830:A831"/>
-    <mergeCell ref="A832:A833"/>
-    <mergeCell ref="A834:A835"/>
-    <mergeCell ref="A836:A837"/>
-    <mergeCell ref="A838:A839"/>
-    <mergeCell ref="A860:A861"/>
-    <mergeCell ref="A862:A863"/>
-    <mergeCell ref="A864:A865"/>
-    <mergeCell ref="A866:A867"/>
-    <mergeCell ref="A868:A869"/>
-    <mergeCell ref="A850:A851"/>
-    <mergeCell ref="A852:A853"/>
-    <mergeCell ref="A854:A855"/>
-    <mergeCell ref="A856:A857"/>
-    <mergeCell ref="A858:A859"/>
-    <mergeCell ref="A891:A892"/>
-    <mergeCell ref="A886:L886"/>
-    <mergeCell ref="A887:L887"/>
-    <mergeCell ref="A893:A894"/>
-    <mergeCell ref="A895:A896"/>
-    <mergeCell ref="A880:A881"/>
-    <mergeCell ref="A882:A883"/>
-    <mergeCell ref="A889:A890"/>
-    <mergeCell ref="A870:A871"/>
-    <mergeCell ref="A872:A873"/>
-    <mergeCell ref="A874:A875"/>
-    <mergeCell ref="A876:A877"/>
-    <mergeCell ref="A878:A879"/>
-    <mergeCell ref="A907:A908"/>
-    <mergeCell ref="A909:A910"/>
-    <mergeCell ref="A911:A912"/>
-    <mergeCell ref="A913:A914"/>
-    <mergeCell ref="A915:A916"/>
-    <mergeCell ref="A897:A898"/>
-    <mergeCell ref="A899:A900"/>
-    <mergeCell ref="A901:A902"/>
-    <mergeCell ref="A903:A904"/>
-    <mergeCell ref="A905:A906"/>
-    <mergeCell ref="A927:A928"/>
-    <mergeCell ref="A929:A930"/>
-    <mergeCell ref="A931:A932"/>
-    <mergeCell ref="A933:A934"/>
-    <mergeCell ref="A935:A936"/>
-    <mergeCell ref="A917:A918"/>
-    <mergeCell ref="A919:A920"/>
-    <mergeCell ref="A921:A922"/>
-    <mergeCell ref="A923:A924"/>
-    <mergeCell ref="A925:A926"/>
-    <mergeCell ref="A947:A948"/>
-    <mergeCell ref="A949:A950"/>
-    <mergeCell ref="A951:A952"/>
-    <mergeCell ref="A953:A954"/>
-    <mergeCell ref="A955:A956"/>
-    <mergeCell ref="A937:A938"/>
-    <mergeCell ref="A939:A940"/>
-    <mergeCell ref="A941:A942"/>
-    <mergeCell ref="A943:A944"/>
-    <mergeCell ref="A945:A946"/>
-    <mergeCell ref="A967:A968"/>
-    <mergeCell ref="A969:A970"/>
-    <mergeCell ref="A971:A972"/>
-    <mergeCell ref="A973:A974"/>
-    <mergeCell ref="A957:A958"/>
-    <mergeCell ref="A959:A960"/>
-    <mergeCell ref="A961:A962"/>
-    <mergeCell ref="A963:A964"/>
-    <mergeCell ref="A965:A966"/>
-    <mergeCell ref="A985:A986"/>
-    <mergeCell ref="A987:A988"/>
-    <mergeCell ref="A989:A990"/>
-    <mergeCell ref="A991:A992"/>
-    <mergeCell ref="A993:A994"/>
-    <mergeCell ref="A975:A976"/>
-    <mergeCell ref="A977:A978"/>
-    <mergeCell ref="A979:A980"/>
-    <mergeCell ref="A981:A982"/>
-    <mergeCell ref="A983:A984"/>
-    <mergeCell ref="A1017:A1018"/>
-    <mergeCell ref="A1019:A1020"/>
-    <mergeCell ref="A1021:A1022"/>
-    <mergeCell ref="A1006:A1007"/>
-    <mergeCell ref="A1013:A1014"/>
-    <mergeCell ref="A1015:A1016"/>
-    <mergeCell ref="A1010:I1010"/>
-    <mergeCell ref="A1011:I1011"/>
-    <mergeCell ref="A995:A996"/>
-    <mergeCell ref="A997:A998"/>
-    <mergeCell ref="A1001:I1001"/>
-    <mergeCell ref="A1002:I1002"/>
-    <mergeCell ref="A1004:A1005"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -25621,28 +25621,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
     </row>
     <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>1582</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -25728,28 +25728,28 @@
       <c r="I7" s="7"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>1585</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -26768,7 +26768,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="B75" s="8"/>
       <c r="C75" s="9">
@@ -26787,10 +26787,10 @@
       <c r="A76" s="16"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -26800,12 +26800,26 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="A57:A58"/>
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A15:A16"/>
@@ -26818,26 +26832,12 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A59:A60"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:I10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26855,31 +26855,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
       <c r="L1" s="10"/>
     </row>
     <row r="2" spans="1:12" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>1658</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
       <c r="J2" s="11"/>
       <c r="K2" s="11"/>
       <c r="L2" s="11"/>
@@ -27738,7 +27738,7 @@
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6" t="s">
-        <v>1712</v>
+        <v>1726</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="6"/>
@@ -27747,28 +27747,28 @@
       <c r="I55" s="7"/>
     </row>
     <row r="58" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="21"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
     </row>
     <row r="59" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="18" t="s">
-        <v>1713</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="20"/>
+      <c r="A59" s="19" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="21"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -27801,7 +27801,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" s="3"/>
@@ -27819,7 +27819,7 @@
       <c r="B62" s="5"/>
       <c r="C62" s="6"/>
       <c r="D62" s="6" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -27829,7 +27829,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="9">
@@ -27848,10 +27848,10 @@
       <c r="A64" s="16"/>
       <c r="B64" s="5"/>
       <c r="C64" s="6" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -27861,31 +27861,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A50:A51"/>
@@ -27893,6 +27868,31 @@
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A58:I58"/>
     <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
